--- a/doc/2026CGJ卡牌设计 - 副本.xlsx
+++ b/doc/2026CGJ卡牌设计 - 副本.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="8_{B7DCBB55-FA52-4FA3-B297-79C789AE9577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A50C4BBD-0302-416F-A699-8B31DC93805E}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{C0502163-791E-4E48-BE7B-C5AD7F0F3EC7}"/>
+    <workbookView windowWidth="23145" windowHeight="8955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,9 +22,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -42,379 +30,629 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
   <si>
     <t>A卡池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>词条</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>内容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B卡池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简洁版</t>
   </si>
   <si>
     <t>初始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>对以连线长度为直径的圆内的肉体和怪物造成5点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>击退所有怪物，对肉体造成4点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连线断裂期间，怪物停止移动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂：使用后，使连线断裂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>放到后面卡池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连线断裂前，你无法出牌。另一位玩家CD为0.5秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你每有一张手牌，另一位玩家造成的下一次伤害翻一倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>血量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击频率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特殊效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自身周围一圈，半径小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>近战，类似冲击波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复生成：使用后，在牌堆里加入一张恢复卡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围伤害</t>
   </si>
   <si>
     <t>初始，另一个玩家打出也会取消</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>你的移速减少，直到双方有牌被打出。你撞到怪物时，对其造成5点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>双方下一张牌打出前，消灭攻击肉体的怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>撞击怪物</t>
   </si>
   <si>
     <t>怪物仍然造成一次伤害
 做一个弹幕从肉体飞到敌人的动画</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双方下一张牌打出前，消灭攻击肉体的怪物</t>
+  </si>
+  <si>
+    <t>反杀怪物</t>
   </si>
   <si>
     <t>消耗</t>
   </si>
   <si>
+    <t>屏幕上所有怪物往左推</t>
+  </si>
+  <si>
+    <t>清场</t>
+  </si>
+  <si>
+    <t>消耗，恢复生成x3，断裂</t>
+  </si>
+  <si>
+    <t>复制卡牌</t>
+  </si>
+  <si>
+    <t>断裂</t>
+  </si>
+  <si>
+    <t>连线恢复前，玩家可以穿墙</t>
+  </si>
+  <si>
+    <t>全屏伤害</t>
+  </si>
+  <si>
+    <t>B卡池</t>
+  </si>
+  <si>
+    <t>击退所有怪物，对肉体造成4点伤害</t>
+  </si>
+  <si>
+    <t>击退</t>
+  </si>
+  <si>
     <t>断裂，消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的CD翻倍，对方的CD减半</t>
+  </si>
+  <si>
+    <t>受伤消灭</t>
+  </si>
+  <si>
+    <t>连线断裂期间，怪物停止移动</t>
+  </si>
+  <si>
+    <t>群体冻结</t>
+  </si>
+  <si>
+    <t>消耗，恢复生成</t>
+  </si>
+  <si>
+    <t>使随机一张手牌失去消耗</t>
+  </si>
+  <si>
+    <t>放到后面卡池</t>
+  </si>
+  <si>
+    <t>连线断裂前，你无法出牌。另一位玩家CD为0.5秒</t>
+  </si>
+  <si>
+    <t>CD减少</t>
+  </si>
+  <si>
+    <t>你每有一张手牌，另一位玩家造成的下一次伤害翻一倍</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>恢复</t>
+  </si>
+  <si>
+    <t>连线期间不能出恢复牌</t>
+  </si>
+  <si>
+    <t>无法出牌时没有CD</t>
+  </si>
+  <si>
+    <t>断裂期间不能出断裂牌</t>
+  </si>
+  <si>
+    <t>恢复生成：使用后，在牌堆里加入一张恢复卡</t>
   </si>
   <si>
     <t>消耗：使用后，</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>简洁版</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>范围伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>撞击怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反杀怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>复制卡牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全屏伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>击退</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受伤消灭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>群体冻结</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CD减少</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂期间不能出断裂牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连线期间不能出恢复牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断裂：使用后，使连线断裂</t>
+  </si>
+  <si>
+    <t>恢复不是消耗</t>
+  </si>
+  <si>
+    <t>敌人</t>
+  </si>
+  <si>
+    <t>引入</t>
+  </si>
+  <si>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>移速</t>
+  </si>
+  <si>
+    <t>体型</t>
+  </si>
+  <si>
+    <t>攻击频率</t>
+  </si>
+  <si>
+    <t>攻击范围</t>
+  </si>
+  <si>
+    <t>攻击方式</t>
+  </si>
+  <si>
+    <t>特殊效果</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>第一个任务点前</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>小</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>自身周围一圈，半径小</t>
+  </si>
+  <si>
+    <t>近战，类似冲击波</t>
+  </si>
+  <si>
+    <t>待机》前往肉体》《攻击》《攻击间隔</t>
+  </si>
+  <si>
+    <t>第二个任务点前</t>
+  </si>
+  <si>
+    <t>同上</t>
+  </si>
+  <si>
+    <t>玩家被打到后，给玩家减速</t>
   </si>
   <si>
     <t>大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法出牌时没有CD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>直线，中等大小的慢速弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>射击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待机》前往肉体》《攻击》《攻击间隔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待机》朝肉体移动》距离够近？》《朝肉体射击》《间隔</t>
   </si>
   <si>
     <t>同上，改成两条平行的弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法正常移动</t>
+  </si>
+  <si>
+    <t>冲撞方向的长方形，较长</t>
   </si>
   <si>
     <t>冲撞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家被打到后，给玩家减速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲撞方向的长方形，较长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法正常移动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲撞前显示前摇</t>
+  </si>
+  <si>
+    <t>待机》前摇》朝肉体冲撞》间隔》前摇</t>
+  </si>
+  <si>
+    <t>第三个任务点前</t>
   </si>
   <si>
     <t>冲撞距离变长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>不适用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>无法移动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>周围十字的弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>向四周持续发射弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际上是机关</t>
   </si>
   <si>
     <t>发射弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>引入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第一个任务点前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第二个任务点前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲撞前显示前摇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待机》前摇》朝肉体冲撞》间隔》前摇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实际上是机关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第三个任务点前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>第三个任务点后是纯精英怪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待机》朝肉体移动》距离够近？》《朝肉体射击》《间隔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屏幕上所有怪物往左移</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复不是消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗，恢复生成x3，断裂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断裂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的CD翻倍，对方的CD减半</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使随机一张手牌失去消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗，恢复生成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连线恢复前，玩家可以穿墙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -422,9 +660,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -436,17 +916,61 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -495,7 +1019,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -528,26 +1052,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -580,23 +1087,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -758,19 +1248,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F053D7-700D-497A-9AE0-D25ADD699BD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
     <col min="3" max="3" width="21.625" customWidth="1"/>
@@ -780,12 +1265,12 @@
     <col min="9" max="9" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -799,10 +1284,10 @@
         <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="B3">
         <v>1</v>
       </c>
@@ -810,85 +1295,85 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
         <v>8</v>
       </c>
-      <c r="J3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:10">
       <c r="B5">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12">
         <v>7</v>
       </c>
@@ -896,353 +1381,353 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="J13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="B17">
         <v>12</v>
       </c>
       <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
         <v>36</v>
       </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
       <c r="J17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="B18" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="C21" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="C22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="C23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="C24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="C25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="C26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="H32" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="J32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E33" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F33" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="H33" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="J33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="I34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B35">
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="G35" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H35" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J35" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B36">
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B37">
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="G37" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="H37" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="I37" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J37" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B38">
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E39" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F39" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N39">
         <f>F3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/doc/2026CGJ卡牌设计 - 副本.xlsx
+++ b/doc/2026CGJ卡牌设计 - 副本.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
   <si>
     <t>A卡池</t>
   </si>
@@ -87,7 +87,7 @@
     <t>消耗，恢复生成x3，断裂</t>
   </si>
   <si>
-    <t>复制卡牌</t>
+    <t>恢复</t>
   </si>
   <si>
     <t>断裂</t>
@@ -96,7 +96,7 @@
     <t>连线恢复前，玩家可以穿墙</t>
   </si>
   <si>
-    <t>全屏伤害</t>
+    <t>穿墙</t>
   </si>
   <si>
     <t>B卡池</t>
@@ -114,7 +114,7 @@
     <t>你的CD翻倍，对方的CD减半</t>
   </si>
   <si>
-    <t>受伤消灭</t>
+    <t>CD分配</t>
   </si>
   <si>
     <t>连线断裂期间，怪物停止移动</t>
@@ -129,22 +129,22 @@
     <t>使随机一张手牌失去消耗</t>
   </si>
   <si>
+    <t>优化手牌</t>
+  </si>
+  <si>
     <t>放到后面卡池</t>
   </si>
   <si>
     <t>连线断裂前，你无法出牌。另一位玩家CD为0.5秒</t>
   </si>
   <si>
-    <t>CD减少</t>
+    <t>集中火力</t>
   </si>
   <si>
     <t>你每有一张手牌，另一位玩家造成的下一次伤害翻一倍</t>
   </si>
   <si>
     <t>增伤</t>
-  </si>
-  <si>
-    <t>恢复</t>
   </si>
   <si>
     <t>连线期间不能出恢复牌</t>
@@ -298,14 +298,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -763,148 +756,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1336,6 +1329,9 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
@@ -1429,7 +1425,7 @@
         <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1437,13 +1433,13 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1454,15 +1450,15 @@
         <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="B18" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>

--- a/doc/2026CGJ卡牌设计 - 副本.xlsx
+++ b/doc/2026CGJ卡牌设计 - 副本.xlsx
@@ -1390,9 +1390,7 @@
       <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
+      <c r="D13"/>
       <c r="E13" t="s">
         <v>27</v>
       </c>
@@ -1448,6 +1446,9 @@
       </c>
       <c r="C17" t="s">
         <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
       </c>
       <c r="E17" t="s">
         <v>37</v>

--- a/doc/2026CGJ卡牌设计 - 副本.xlsx
+++ b/doc/2026CGJ卡牌设计 - 副本.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_F58679C4259DFD81ECECE05CC9D06DC3A746F921" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{413472C6-FF82-43A0-BC34-23AA5DF33B5F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23145" windowHeight="8955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,6 +59,9 @@
     <t>初始，另一个玩家打出也会取消</t>
   </si>
   <si>
+    <t>你的移速减少，直到双方有牌被打出。你撞到怪物时，对其造成4点伤害</t>
+  </si>
+  <si>
     <t>撞击怪物</t>
   </si>
   <si>
@@ -81,6 +78,9 @@
     <t>消耗</t>
   </si>
   <si>
+    <t>屏幕上所有怪物往左推</t>
+  </si>
+  <si>
     <t>清场</t>
   </si>
   <si>
@@ -198,6 +198,15 @@
     <t>第一个任务点前</t>
   </si>
   <si>
+    <t>玩家0.6倍</t>
+  </si>
+  <si>
+    <t>3秒一次</t>
+  </si>
+  <si>
+    <t>以自身为原点，半径为自身直径的圆</t>
+  </si>
+  <si>
     <t>近战，类似冲击波</t>
   </si>
   <si>
@@ -210,12 +219,30 @@
     <t>玩家被打到后，给玩家减速</t>
   </si>
   <si>
+    <t>玩家1.5倍</t>
+  </si>
+  <si>
+    <t>2秒一次</t>
+  </si>
+  <si>
+    <t>关卡宽度1.5倍长的直线，自身一般=半大小的慢速弹幕</t>
+  </si>
+  <si>
     <t>射击</t>
   </si>
   <si>
     <t>待机》朝肉体移动》距离够近？》《朝肉体射击》《间隔</t>
   </si>
   <si>
+    <t>同上，改成两条平行的弹幕</t>
+  </si>
+  <si>
+    <t>玩家大小</t>
+  </si>
+  <si>
+    <t>冲撞方向的长方形，玩家的三倍长。可以往右冲，但是离自己的生成点太远了会停下</t>
+  </si>
+  <si>
     <t>冲撞</t>
   </si>
   <si>
@@ -228,6 +255,18 @@
     <t>第三个任务点前</t>
   </si>
   <si>
+    <t>1.5秒一次</t>
+  </si>
+  <si>
+    <t>冲撞距离变长1.5倍</t>
+  </si>
+  <si>
+    <t>不适用，无法移动</t>
+  </si>
+  <si>
+    <t>自身周围十字的弹幕</t>
+  </si>
+  <si>
     <t>向四周持续发射弹幕</t>
   </si>
   <si>
@@ -238,73 +277,19 @@
   </si>
   <si>
     <t>第三个任务点后是纯精英怪</t>
-  </si>
-  <si>
-    <t>屏幕上所有怪物往左推</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你的移速减少，直到双方有牌被打出。你撞到怪物时，对其造成4点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不适用，无法移动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家1.5倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家大小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家0.6倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5秒一次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2秒一次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3秒一次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>以自身为原点，半径为自身直径的圆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡宽度1.5倍长的直线，自身一般=半大小的慢速弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上，改成两条平行的弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲撞方向的长方形，玩家的三倍长。可以往右冲，但是离自己的生成点太远了会停下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冲撞距离变长1.5倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自身周围十字的弹幕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,30 +298,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -344,9 +651,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -354,24 +903,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -649,14 +1242,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
     <col min="3" max="3" width="21.625" customWidth="1"/>
@@ -666,12 +1259,12 @@
     <col min="9" max="9" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -688,7 +1281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="B3">
         <v>1</v>
       </c>
@@ -702,82 +1295,82 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>69</v>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:10">
       <c r="B5">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>68</v>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12">
         <v>7</v>
       </c>
@@ -785,163 +1378,163 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="B16">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="B17">
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="B18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="C21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="C22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="C23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="C24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="C25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="C26" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H32" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I32" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -949,25 +1542,25 @@
       <c r="C33">
         <v>5</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>77</v>
+      <c r="E33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="H33" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -976,12 +1569,12 @@
         <v>9</v>
       </c>
       <c r="I34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -989,25 +1582,25 @@
       <c r="C35">
         <v>4</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>78</v>
+      <c r="E35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1015,13 +1608,13 @@
       <c r="C36">
         <v>5</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="G36" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B37">
         <v>5</v>
@@ -1029,28 +1622,28 @@
       <c r="C37">
         <v>8</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H37" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37" t="s">
         <v>72</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H37" t="s">
-        <v>60</v>
-      </c>
-      <c r="I37" t="s">
-        <v>61</v>
-      </c>
       <c r="J37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1058,56 +1651,56 @@
       <c r="C38">
         <v>11</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="E38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B39">
         <v>7</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>82</v>
+      <c r="C39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="H39" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I39" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="J39" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="N39">
         <f>F3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>